--- a/templates/signa_decir_brigade_template.xlsx
+++ b/templates/signa_decir_brigade_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48B7F49E-379E-460E-861E-CC641C9A21FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBE95AE-C373-4AC7-8459-64AA3519715F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51E76821-7103-4E88-A13D-BD34C9109D49}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="20">
   <si>
     <t>REGISTO PRESENÇAS</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>Anexo V à NOP 2101/2026– DECIR</t>
+  </si>
+  <si>
+    <t>ECIN 01</t>
+  </si>
+  <si>
+    <t>ECIN 02</t>
   </si>
 </sst>
 </file>
@@ -369,74 +375,74 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -965,110 +971,110 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
     </row>
     <row r="4" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
+      <c r="B12" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25" t="s">
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
       <c r="I13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1081,11 +1087,11 @@
       <c r="C14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
@@ -1094,86 +1100,86 @@
       <c r="C15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="32"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="7"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="7"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
     </row>
     <row r="19" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
+      <c r="B21" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25" t="s">
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1186,11 +1192,11 @@
       <c r="C23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
     </row>
@@ -1199,86 +1205,86 @@
       <c r="C24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="32"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="10"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="C26" s="10"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
     <row r="28" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25" t="s">
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
       <c r="I31" s="2" t="s">
         <v>6</v>
       </c>
@@ -1291,11 +1297,11 @@
       <c r="C32" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
     </row>
@@ -1304,86 +1310,86 @@
       <c r="C33" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="C35" s="10"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="32"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="32"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
     <row r="37" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
+      <c r="B39" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25" t="s">
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
       <c r="I40" s="2" t="s">
         <v>6</v>
       </c>
@@ -1396,11 +1402,11 @@
       <c r="C41" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="29"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="32"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="22"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
     </row>
@@ -1409,44 +1415,44 @@
       <c r="C42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="29"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="32"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="22"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="32"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="22"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="32"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="22"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="32"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="22"/>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
     </row>
@@ -1458,41 +1464,41 @@
     </row>
     <row r="48" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="19"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="25"/>
     </row>
     <row r="50" spans="2:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="20"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="22"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="28"/>
     </row>
     <row r="51" spans="2:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="34" t="s">
+      <c r="B51" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
     </row>
     <row r="52" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
@@ -1504,474 +1510,474 @@
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F55" s="26" t="s">
+      <c r="F55" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
     </row>
     <row r="57" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
     </row>
     <row r="59" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
     </row>
     <row r="61" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28"/>
-      <c r="J62" s="28"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
     </row>
     <row r="63" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="23"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B65" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-      <c r="H65" s="24"/>
-      <c r="I65" s="24"/>
-      <c r="J65" s="24"/>
+      <c r="B65" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C66" s="25" t="s">
+      <c r="C66" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25" t="s">
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="7"/>
       <c r="C67" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="7"/>
       <c r="C68" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="31"/>
+      <c r="I68" s="31"/>
+      <c r="J68" s="31"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="7"/>
       <c r="C69" s="8"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="7"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="31"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="31"/>
     </row>
     <row r="72" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="73" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B73" s="23"/>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="23"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B74" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="24"/>
-      <c r="J74" s="24"/>
+      <c r="B74" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="25" t="s">
+      <c r="C75" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25" t="s">
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25"/>
-      <c r="I75" s="25"/>
-      <c r="J75" s="25"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="7"/>
       <c r="C76" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="13"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="31"/>
+      <c r="J76" s="31"/>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="7"/>
       <c r="C77" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D77" s="13"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
+      <c r="J77" s="31"/>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="7"/>
       <c r="C78" s="8"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="31"/>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
+      <c r="J79" s="31"/>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="31"/>
+      <c r="I80" s="31"/>
+      <c r="J80" s="31"/>
     </row>
     <row r="81" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
-      <c r="G82" s="23"/>
-      <c r="H82" s="23"/>
-      <c r="I82" s="23"/>
-      <c r="J82" s="23"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B83" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C83" s="24"/>
-      <c r="D83" s="24"/>
-      <c r="E83" s="24"/>
-      <c r="F83" s="24"/>
-      <c r="G83" s="24"/>
-      <c r="H83" s="24"/>
-      <c r="I83" s="24"/>
-      <c r="J83" s="24"/>
+      <c r="B83" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="25" t="s">
+      <c r="C84" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25" t="s">
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="25"/>
-      <c r="J84" s="25"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="7"/>
       <c r="C85" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D85" s="13"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="15"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="31"/>
+      <c r="G85" s="31"/>
+      <c r="H85" s="31"/>
+      <c r="I85" s="31"/>
+      <c r="J85" s="31"/>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="7"/>
       <c r="C86" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D86" s="13"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="15"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31"/>
+      <c r="H86" s="31"/>
+      <c r="I86" s="31"/>
+      <c r="J86" s="31"/>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="15"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
+      <c r="J87" s="31"/>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="7"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="15"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="31"/>
+      <c r="H88" s="31"/>
+      <c r="I88" s="31"/>
+      <c r="J88" s="31"/>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="15"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="31"/>
+      <c r="G89" s="31"/>
+      <c r="H89" s="31"/>
+      <c r="I89" s="31"/>
+      <c r="J89" s="31"/>
     </row>
     <row r="90" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" s="23"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="23"/>
-      <c r="E91" s="23"/>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
-      <c r="H91" s="23"/>
-      <c r="I91" s="23"/>
-      <c r="J91" s="23"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="19"/>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="19"/>
+      <c r="I91" s="19"/>
+      <c r="J91" s="19"/>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B92" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C92" s="24"/>
-      <c r="D92" s="24"/>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="24"/>
-      <c r="J92" s="24"/>
+      <c r="B92" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C93" s="25" t="s">
+      <c r="C93" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="25"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25" t="s">
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="25"/>
-      <c r="J93" s="25"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="7"/>
       <c r="C94" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="15"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="31"/>
+      <c r="G94" s="31"/>
+      <c r="H94" s="31"/>
+      <c r="I94" s="31"/>
+      <c r="J94" s="31"/>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="7"/>
       <c r="C95" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="31"/>
+      <c r="G95" s="31"/>
+      <c r="H95" s="31"/>
+      <c r="I95" s="31"/>
+      <c r="J95" s="31"/>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="7"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="31"/>
+      <c r="G96" s="31"/>
+      <c r="H96" s="31"/>
+      <c r="I96" s="31"/>
+      <c r="J96" s="31"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="7"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="31"/>
+      <c r="G97" s="31"/>
+      <c r="H97" s="31"/>
+      <c r="I97" s="31"/>
+      <c r="J97" s="31"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="7"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="31"/>
+      <c r="G98" s="31"/>
+      <c r="H98" s="31"/>
+      <c r="I98" s="31"/>
+      <c r="J98" s="31"/>
     </row>
     <row r="99" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="100" spans="2:10" x14ac:dyDescent="0.25">
@@ -1980,41 +1986,41 @@
       </c>
     </row>
     <row r="101" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C101" s="16"/>
-      <c r="D101" s="16"/>
-      <c r="E101" s="16"/>
-      <c r="F101" s="16"/>
-      <c r="G101" s="16"/>
-      <c r="H101" s="16"/>
-      <c r="I101" s="16"/>
-      <c r="J101" s="16"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="32"/>
+      <c r="J101" s="32"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B102" s="17" t="s">
+      <c r="B102" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
-      <c r="G102" s="18"/>
-      <c r="H102" s="18"/>
-      <c r="I102" s="18"/>
-      <c r="J102" s="19"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="24"/>
+      <c r="I102" s="24"/>
+      <c r="J102" s="25"/>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B103" s="20"/>
-      <c r="C103" s="21"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
-      <c r="I103" s="21"/>
-      <c r="J103" s="22"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="27"/>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="27"/>
+      <c r="H103" s="27"/>
+      <c r="I103" s="27"/>
+      <c r="J103" s="28"/>
     </row>
     <row r="104" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="33" t="s">
@@ -2041,58 +2047,58 @@
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F108" s="26" t="s">
+      <c r="F108" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="G108" s="26"/>
-      <c r="H108" s="26"/>
-      <c r="I108" s="26"/>
-      <c r="J108" s="26"/>
+      <c r="G108" s="17"/>
+      <c r="H108" s="17"/>
+      <c r="I108" s="17"/>
+      <c r="J108" s="17"/>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F109" s="26"/>
-      <c r="G109" s="26"/>
-      <c r="H109" s="26"/>
-      <c r="I109" s="26"/>
-      <c r="J109" s="26"/>
+      <c r="F109" s="17"/>
+      <c r="G109" s="17"/>
+      <c r="H109" s="17"/>
+      <c r="I109" s="17"/>
+      <c r="J109" s="17"/>
     </row>
     <row r="110" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="111" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C111" s="27"/>
-      <c r="D111" s="27"/>
-      <c r="E111" s="27"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="27"/>
-      <c r="H111" s="27"/>
-      <c r="I111" s="27"/>
-      <c r="J111" s="27"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="16"/>
+      <c r="J111" s="16"/>
     </row>
     <row r="112" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C112" s="27"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
-      <c r="J112" s="27"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16"/>
+      <c r="I112" s="16"/>
+      <c r="J112" s="16"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B113" s="28"/>
-      <c r="C113" s="28"/>
-      <c r="D113" s="28"/>
-      <c r="E113" s="28"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="28"/>
-      <c r="H113" s="28"/>
-      <c r="I113" s="28"/>
-      <c r="J113" s="28"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="18"/>
+      <c r="J113" s="18"/>
     </row>
     <row r="114" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="1"/>
@@ -2106,55 +2112,55 @@
       <c r="J114" s="1"/>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B115" s="28"/>
-      <c r="C115" s="28"/>
-      <c r="D115" s="28"/>
-      <c r="E115" s="28"/>
-      <c r="F115" s="28"/>
-      <c r="G115" s="28"/>
-      <c r="H115" s="28"/>
-      <c r="I115" s="28"/>
-      <c r="J115" s="28"/>
+      <c r="B115" s="18"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="18"/>
+      <c r="G115" s="18"/>
+      <c r="H115" s="18"/>
+      <c r="I115" s="18"/>
+      <c r="J115" s="18"/>
     </row>
     <row r="116" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="117" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B117" s="23"/>
-      <c r="C117" s="23"/>
-      <c r="D117" s="23"/>
-      <c r="E117" s="23"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
-      <c r="H117" s="23"/>
-      <c r="I117" s="23"/>
-      <c r="J117" s="23"/>
+      <c r="B117" s="19"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
+      <c r="F117" s="19"/>
+      <c r="G117" s="19"/>
+      <c r="H117" s="19"/>
+      <c r="I117" s="19"/>
+      <c r="J117" s="19"/>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B118" s="24" t="s">
+      <c r="B118" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C118" s="24"/>
-      <c r="D118" s="24"/>
-      <c r="E118" s="24"/>
-      <c r="F118" s="24"/>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="24"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="12"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C119" s="25" t="s">
+      <c r="C119" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="25"/>
-      <c r="E119" s="25"/>
-      <c r="F119" s="25" t="s">
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G119" s="25"/>
-      <c r="H119" s="25"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
       <c r="I119" s="2" t="s">
         <v>6</v>
       </c>
@@ -2167,11 +2173,11 @@
       <c r="C120" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D120" s="29"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="30"/>
-      <c r="G120" s="31"/>
-      <c r="H120" s="32"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="20"/>
+      <c r="G120" s="21"/>
+      <c r="H120" s="22"/>
       <c r="I120" s="7"/>
       <c r="J120" s="7"/>
     </row>
@@ -2180,53 +2186,53 @@
       <c r="C121" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D121" s="29"/>
-      <c r="E121" s="13"/>
-      <c r="F121" s="30"/>
-      <c r="G121" s="31"/>
-      <c r="H121" s="32"/>
+      <c r="D121" s="14"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="21"/>
+      <c r="H121" s="22"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
     </row>
     <row r="122" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="123" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B123" s="23"/>
-      <c r="C123" s="23"/>
-      <c r="D123" s="23"/>
-      <c r="E123" s="23"/>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="23"/>
+      <c r="B123" s="19"/>
+      <c r="C123" s="19"/>
+      <c r="D123" s="19"/>
+      <c r="E123" s="19"/>
+      <c r="F123" s="19"/>
+      <c r="G123" s="19"/>
+      <c r="H123" s="19"/>
+      <c r="I123" s="19"/>
+      <c r="J123" s="19"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B124" s="24" t="s">
+      <c r="B124" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C124" s="24"/>
-      <c r="D124" s="24"/>
-      <c r="E124" s="24"/>
-      <c r="F124" s="24"/>
-      <c r="G124" s="24"/>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="24"/>
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C125" s="25" t="s">
+      <c r="C125" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="25"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="25" t="s">
+      <c r="D125" s="13"/>
+      <c r="E125" s="13"/>
+      <c r="F125" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
       <c r="I125" s="2" t="s">
         <v>6</v>
       </c>
@@ -2239,11 +2245,11 @@
       <c r="C126" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D126" s="29"/>
-      <c r="E126" s="13"/>
-      <c r="F126" s="30"/>
-      <c r="G126" s="31"/>
-      <c r="H126" s="32"/>
+      <c r="D126" s="14"/>
+      <c r="E126" s="15"/>
+      <c r="F126" s="20"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="22"/>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
     </row>
@@ -2252,11 +2258,11 @@
       <c r="C127" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D127" s="29"/>
-      <c r="E127" s="13"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="31"/>
-      <c r="H127" s="32"/>
+      <c r="D127" s="14"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="22"/>
       <c r="I127" s="7"/>
       <c r="J127" s="7"/>
     </row>
@@ -2268,41 +2274,41 @@
     </row>
     <row r="130" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="131" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B131" s="17" t="s">
+      <c r="B131" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="18"/>
-      <c r="H131" s="18"/>
-      <c r="I131" s="18"/>
-      <c r="J131" s="19"/>
+      <c r="C131" s="24"/>
+      <c r="D131" s="24"/>
+      <c r="E131" s="24"/>
+      <c r="F131" s="24"/>
+      <c r="G131" s="24"/>
+      <c r="H131" s="24"/>
+      <c r="I131" s="24"/>
+      <c r="J131" s="25"/>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B132" s="20"/>
-      <c r="C132" s="21"/>
-      <c r="D132" s="21"/>
-      <c r="E132" s="21"/>
-      <c r="F132" s="21"/>
-      <c r="G132" s="21"/>
-      <c r="H132" s="21"/>
-      <c r="I132" s="21"/>
-      <c r="J132" s="22"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="27"/>
+      <c r="D132" s="27"/>
+      <c r="E132" s="27"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
+      <c r="H132" s="27"/>
+      <c r="I132" s="27"/>
+      <c r="J132" s="28"/>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B133" s="12" t="s">
+      <c r="B133" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C133" s="12"/>
-      <c r="D133" s="12"/>
-      <c r="E133" s="12"/>
-      <c r="F133" s="12"/>
-      <c r="G133" s="12"/>
-      <c r="H133" s="12"/>
-      <c r="I133" s="12"/>
-      <c r="J133" s="12"/>
+      <c r="C133" s="34"/>
+      <c r="D133" s="34"/>
+      <c r="E133" s="34"/>
+      <c r="F133" s="34"/>
+      <c r="G133" s="34"/>
+      <c r="H133" s="34"/>
+      <c r="I133" s="34"/>
+      <c r="J133" s="34"/>
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="159" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2315,206 +2321,206 @@
       </c>
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F162" s="26" t="s">
+      <c r="F162" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="G162" s="26"/>
-      <c r="H162" s="26"/>
-      <c r="I162" s="26"/>
-      <c r="J162" s="26"/>
+      <c r="G162" s="17"/>
+      <c r="H162" s="17"/>
+      <c r="I162" s="17"/>
+      <c r="J162" s="17"/>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F163" s="26"/>
-      <c r="G163" s="26"/>
-      <c r="H163" s="26"/>
-      <c r="I163" s="26"/>
-      <c r="J163" s="26"/>
+      <c r="F163" s="17"/>
+      <c r="G163" s="17"/>
+      <c r="H163" s="17"/>
+      <c r="I163" s="17"/>
+      <c r="J163" s="17"/>
     </row>
     <row r="164" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="165" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="27" t="s">
+      <c r="B165" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C165" s="27"/>
-      <c r="D165" s="27"/>
-      <c r="E165" s="27"/>
-      <c r="F165" s="27"/>
-      <c r="G165" s="27"/>
-      <c r="H165" s="27"/>
-      <c r="I165" s="27"/>
-      <c r="J165" s="27"/>
+      <c r="C165" s="16"/>
+      <c r="D165" s="16"/>
+      <c r="E165" s="16"/>
+      <c r="F165" s="16"/>
+      <c r="G165" s="16"/>
+      <c r="H165" s="16"/>
+      <c r="I165" s="16"/>
+      <c r="J165" s="16"/>
     </row>
     <row r="166" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="27" t="s">
+      <c r="B166" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C166" s="27"/>
-      <c r="D166" s="27"/>
-      <c r="E166" s="27"/>
-      <c r="F166" s="27"/>
-      <c r="G166" s="27"/>
-      <c r="H166" s="27"/>
-      <c r="I166" s="27"/>
-      <c r="J166" s="27"/>
+      <c r="C166" s="16"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="16"/>
+      <c r="F166" s="16"/>
+      <c r="G166" s="16"/>
+      <c r="H166" s="16"/>
+      <c r="I166" s="16"/>
+      <c r="J166" s="16"/>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B167" s="28"/>
-      <c r="C167" s="28"/>
-      <c r="D167" s="28"/>
-      <c r="E167" s="28"/>
-      <c r="F167" s="28"/>
-      <c r="G167" s="28"/>
-      <c r="H167" s="28"/>
-      <c r="I167" s="28"/>
-      <c r="J167" s="28"/>
+      <c r="B167" s="18"/>
+      <c r="C167" s="18"/>
+      <c r="D167" s="18"/>
+      <c r="E167" s="18"/>
+      <c r="F167" s="18"/>
+      <c r="G167" s="18"/>
+      <c r="H167" s="18"/>
+      <c r="I167" s="18"/>
+      <c r="J167" s="18"/>
     </row>
     <row r="168" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="169" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B169" s="28"/>
-      <c r="C169" s="28"/>
-      <c r="D169" s="28"/>
-      <c r="E169" s="28"/>
-      <c r="F169" s="28"/>
-      <c r="G169" s="28"/>
-      <c r="H169" s="28"/>
-      <c r="I169" s="28"/>
-      <c r="J169" s="28"/>
+      <c r="B169" s="18"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="18"/>
+      <c r="E169" s="18"/>
+      <c r="F169" s="18"/>
+      <c r="G169" s="18"/>
+      <c r="H169" s="18"/>
+      <c r="I169" s="18"/>
+      <c r="J169" s="18"/>
     </row>
     <row r="170" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="171" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B171" s="23"/>
-      <c r="C171" s="23"/>
-      <c r="D171" s="23"/>
-      <c r="E171" s="23"/>
-      <c r="F171" s="23"/>
-      <c r="G171" s="23"/>
-      <c r="H171" s="23"/>
-      <c r="I171" s="23"/>
-      <c r="J171" s="23"/>
+      <c r="B171" s="19"/>
+      <c r="C171" s="19"/>
+      <c r="D171" s="19"/>
+      <c r="E171" s="19"/>
+      <c r="F171" s="19"/>
+      <c r="G171" s="19"/>
+      <c r="H171" s="19"/>
+      <c r="I171" s="19"/>
+      <c r="J171" s="19"/>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B172" s="24" t="s">
+      <c r="B172" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C172" s="24"/>
-      <c r="D172" s="24"/>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="24"/>
+      <c r="C172" s="12"/>
+      <c r="D172" s="12"/>
+      <c r="E172" s="12"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="12"/>
+      <c r="H172" s="12"/>
+      <c r="I172" s="12"/>
+      <c r="J172" s="12"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C173" s="25" t="s">
+      <c r="C173" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="25"/>
-      <c r="E173" s="25"/>
-      <c r="F173" s="25" t="s">
+      <c r="D173" s="13"/>
+      <c r="E173" s="13"/>
+      <c r="F173" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G173" s="25"/>
-      <c r="H173" s="25"/>
-      <c r="I173" s="25"/>
-      <c r="J173" s="25"/>
+      <c r="G173" s="13"/>
+      <c r="H173" s="13"/>
+      <c r="I173" s="13"/>
+      <c r="J173" s="13"/>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="7"/>
       <c r="C174" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D174" s="13"/>
-      <c r="E174" s="14"/>
-      <c r="F174" s="15"/>
-      <c r="G174" s="15"/>
-      <c r="H174" s="15"/>
-      <c r="I174" s="15"/>
-      <c r="J174" s="15"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="30"/>
+      <c r="F174" s="31"/>
+      <c r="G174" s="31"/>
+      <c r="H174" s="31"/>
+      <c r="I174" s="31"/>
+      <c r="J174" s="31"/>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="7"/>
       <c r="C175" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D175" s="13"/>
-      <c r="E175" s="14"/>
-      <c r="F175" s="15"/>
-      <c r="G175" s="15"/>
-      <c r="H175" s="15"/>
-      <c r="I175" s="15"/>
-      <c r="J175" s="15"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="30"/>
+      <c r="F175" s="31"/>
+      <c r="G175" s="31"/>
+      <c r="H175" s="31"/>
+      <c r="I175" s="31"/>
+      <c r="J175" s="31"/>
     </row>
     <row r="176" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="177" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B177" s="23"/>
-      <c r="C177" s="23"/>
-      <c r="D177" s="23"/>
-      <c r="E177" s="23"/>
-      <c r="F177" s="23"/>
-      <c r="G177" s="23"/>
-      <c r="H177" s="23"/>
-      <c r="I177" s="23"/>
-      <c r="J177" s="23"/>
+      <c r="B177" s="19"/>
+      <c r="C177" s="19"/>
+      <c r="D177" s="19"/>
+      <c r="E177" s="19"/>
+      <c r="F177" s="19"/>
+      <c r="G177" s="19"/>
+      <c r="H177" s="19"/>
+      <c r="I177" s="19"/>
+      <c r="J177" s="19"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B178" s="24" t="s">
+      <c r="B178" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C178" s="24"/>
-      <c r="D178" s="24"/>
-      <c r="E178" s="24"/>
-      <c r="F178" s="24"/>
-      <c r="G178" s="24"/>
-      <c r="H178" s="24"/>
-      <c r="I178" s="24"/>
-      <c r="J178" s="24"/>
+      <c r="C178" s="12"/>
+      <c r="D178" s="12"/>
+      <c r="E178" s="12"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12"/>
+      <c r="H178" s="12"/>
+      <c r="I178" s="12"/>
+      <c r="J178" s="12"/>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C179" s="25" t="s">
+      <c r="C179" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="25"/>
-      <c r="E179" s="25"/>
-      <c r="F179" s="25" t="s">
+      <c r="D179" s="13"/>
+      <c r="E179" s="13"/>
+      <c r="F179" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G179" s="25"/>
-      <c r="H179" s="25"/>
-      <c r="I179" s="25"/>
-      <c r="J179" s="25"/>
+      <c r="G179" s="13"/>
+      <c r="H179" s="13"/>
+      <c r="I179" s="13"/>
+      <c r="J179" s="13"/>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="7"/>
       <c r="C180" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D180" s="13"/>
-      <c r="E180" s="14"/>
-      <c r="F180" s="15"/>
-      <c r="G180" s="15"/>
-      <c r="H180" s="15"/>
-      <c r="I180" s="15"/>
-      <c r="J180" s="15"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="30"/>
+      <c r="F180" s="31"/>
+      <c r="G180" s="31"/>
+      <c r="H180" s="31"/>
+      <c r="I180" s="31"/>
+      <c r="J180" s="31"/>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="7"/>
       <c r="C181" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D181" s="13"/>
-      <c r="E181" s="14"/>
-      <c r="F181" s="15"/>
-      <c r="G181" s="15"/>
-      <c r="H181" s="15"/>
-      <c r="I181" s="15"/>
-      <c r="J181" s="15"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="30"/>
+      <c r="F181" s="31"/>
+      <c r="G181" s="31"/>
+      <c r="H181" s="31"/>
+      <c r="I181" s="31"/>
+      <c r="J181" s="31"/>
     </row>
     <row r="182" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="183" spans="2:10" x14ac:dyDescent="0.25">
@@ -2523,54 +2529,54 @@
       </c>
     </row>
     <row r="184" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="16" t="s">
+      <c r="B184" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C184" s="16"/>
-      <c r="D184" s="16"/>
-      <c r="E184" s="16"/>
-      <c r="F184" s="16"/>
-      <c r="G184" s="16"/>
-      <c r="H184" s="16"/>
-      <c r="I184" s="16"/>
-      <c r="J184" s="16"/>
+      <c r="C184" s="32"/>
+      <c r="D184" s="32"/>
+      <c r="E184" s="32"/>
+      <c r="F184" s="32"/>
+      <c r="G184" s="32"/>
+      <c r="H184" s="32"/>
+      <c r="I184" s="32"/>
+      <c r="J184" s="32"/>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B185" s="17" t="s">
+      <c r="B185" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C185" s="18"/>
-      <c r="D185" s="18"/>
-      <c r="E185" s="18"/>
-      <c r="F185" s="18"/>
-      <c r="G185" s="18"/>
-      <c r="H185" s="18"/>
-      <c r="I185" s="18"/>
-      <c r="J185" s="19"/>
+      <c r="C185" s="24"/>
+      <c r="D185" s="24"/>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="24"/>
+      <c r="J185" s="25"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B186" s="20"/>
-      <c r="C186" s="21"/>
-      <c r="D186" s="21"/>
-      <c r="E186" s="21"/>
-      <c r="F186" s="21"/>
-      <c r="G186" s="21"/>
-      <c r="H186" s="21"/>
-      <c r="I186" s="21"/>
-      <c r="J186" s="22"/>
+      <c r="B186" s="26"/>
+      <c r="C186" s="27"/>
+      <c r="D186" s="27"/>
+      <c r="E186" s="27"/>
+      <c r="F186" s="27"/>
+      <c r="G186" s="27"/>
+      <c r="H186" s="27"/>
+      <c r="I186" s="27"/>
+      <c r="J186" s="28"/>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B187" s="12" t="s">
+      <c r="B187" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C187" s="12"/>
-      <c r="D187" s="12"/>
-      <c r="E187" s="12"/>
-      <c r="F187" s="12"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="12"/>
-      <c r="I187" s="12"/>
-      <c r="J187" s="12"/>
+      <c r="C187" s="34"/>
+      <c r="D187" s="34"/>
+      <c r="E187" s="34"/>
+      <c r="F187" s="34"/>
+      <c r="G187" s="34"/>
+      <c r="H187" s="34"/>
+      <c r="I187" s="34"/>
+      <c r="J187" s="34"/>
     </row>
     <row r="211" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="212" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2584,6 +2590,178 @@
     </row>
   </sheetData>
   <mergeCells count="186">
+    <mergeCell ref="C179:E179"/>
+    <mergeCell ref="F179:J179"/>
+    <mergeCell ref="D180:E180"/>
+    <mergeCell ref="F180:J180"/>
+    <mergeCell ref="D181:E181"/>
+    <mergeCell ref="F181:J181"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="B184:J184"/>
+    <mergeCell ref="B185:J186"/>
+    <mergeCell ref="F177:J177"/>
+    <mergeCell ref="B177:E177"/>
+    <mergeCell ref="B178:J178"/>
+    <mergeCell ref="B172:J172"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="F173:J173"/>
+    <mergeCell ref="D174:E174"/>
+    <mergeCell ref="F174:J174"/>
+    <mergeCell ref="D175:E175"/>
+    <mergeCell ref="F175:J175"/>
+    <mergeCell ref="F162:J163"/>
+    <mergeCell ref="B165:J165"/>
+    <mergeCell ref="B166:J166"/>
+    <mergeCell ref="B167:J167"/>
+    <mergeCell ref="B169:J169"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="F171:J171"/>
+    <mergeCell ref="B131:J132"/>
+    <mergeCell ref="B133:J133"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="D126:E126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="D127:E127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="F123:J123"/>
+    <mergeCell ref="B124:J124"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="D120:E120"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="D121:E121"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="B113:J113"/>
+    <mergeCell ref="B115:J115"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="F117:J117"/>
+    <mergeCell ref="B118:J118"/>
+    <mergeCell ref="B101:J101"/>
+    <mergeCell ref="B102:J103"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="F108:J109"/>
+    <mergeCell ref="B111:J111"/>
+    <mergeCell ref="B112:J112"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:J96"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:J97"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:J98"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="F93:J93"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="F94:J94"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:J95"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:J88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:J89"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="F91:J91"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="F85:J85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F86:J86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:J87"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:J80"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="F82:J82"/>
+    <mergeCell ref="B83:J83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="F84:J84"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="F77:J77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:J78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:J79"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="F73:J73"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="F75:J75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:J76"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="F67:J67"/>
+    <mergeCell ref="F68:J68"/>
+    <mergeCell ref="F69:J69"/>
+    <mergeCell ref="F70:J70"/>
+    <mergeCell ref="F71:J71"/>
+    <mergeCell ref="B62:J62"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="F64:J64"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="F66:J66"/>
+    <mergeCell ref="B49:J50"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="F55:J56"/>
+    <mergeCell ref="B58:J58"/>
+    <mergeCell ref="B59:J59"/>
+    <mergeCell ref="B60:J60"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:J29"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="B12:J12"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="F13:H13"/>
@@ -2598,178 +2776,6 @@
     <mergeCell ref="F11:J11"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="F15:H15"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="F38:J38"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="B62:J62"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="F64:J64"/>
-    <mergeCell ref="B65:J65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="F66:J66"/>
-    <mergeCell ref="B49:J50"/>
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="F55:J56"/>
-    <mergeCell ref="B58:J58"/>
-    <mergeCell ref="B59:J59"/>
-    <mergeCell ref="B60:J60"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="F67:J67"/>
-    <mergeCell ref="F68:J68"/>
-    <mergeCell ref="F69:J69"/>
-    <mergeCell ref="F70:J70"/>
-    <mergeCell ref="F71:J71"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="F77:J77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:J78"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="F79:J79"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="F73:J73"/>
-    <mergeCell ref="B74:J74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="F75:J75"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:J76"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="F85:J85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F86:J86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:J87"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:J80"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="F82:J82"/>
-    <mergeCell ref="B83:J83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="F84:J84"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="F93:J93"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="F94:J94"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="F95:J95"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:J88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:J89"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="F91:J91"/>
-    <mergeCell ref="B101:J101"/>
-    <mergeCell ref="B102:J103"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="F108:J109"/>
-    <mergeCell ref="B111:J111"/>
-    <mergeCell ref="B112:J112"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="F96:J96"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="F97:J97"/>
-    <mergeCell ref="D98:E98"/>
-    <mergeCell ref="F98:J98"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="D120:E120"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="D121:E121"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="B113:J113"/>
-    <mergeCell ref="B115:J115"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="F117:J117"/>
-    <mergeCell ref="B118:J118"/>
-    <mergeCell ref="C125:E125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="D126:E126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="D127:E127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="F123:J123"/>
-    <mergeCell ref="B124:J124"/>
-    <mergeCell ref="F162:J163"/>
-    <mergeCell ref="B165:J165"/>
-    <mergeCell ref="B166:J166"/>
-    <mergeCell ref="B167:J167"/>
-    <mergeCell ref="B169:J169"/>
-    <mergeCell ref="B171:E171"/>
-    <mergeCell ref="F171:J171"/>
-    <mergeCell ref="B131:J132"/>
-    <mergeCell ref="B133:J133"/>
-    <mergeCell ref="F177:J177"/>
-    <mergeCell ref="B177:E177"/>
-    <mergeCell ref="B178:J178"/>
-    <mergeCell ref="B172:J172"/>
-    <mergeCell ref="C173:E173"/>
-    <mergeCell ref="F173:J173"/>
-    <mergeCell ref="D174:E174"/>
-    <mergeCell ref="F174:J174"/>
-    <mergeCell ref="D175:E175"/>
-    <mergeCell ref="F175:J175"/>
-    <mergeCell ref="C179:E179"/>
-    <mergeCell ref="F179:J179"/>
-    <mergeCell ref="D180:E180"/>
-    <mergeCell ref="F180:J180"/>
-    <mergeCell ref="D181:E181"/>
-    <mergeCell ref="F181:J181"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="B184:J184"/>
-    <mergeCell ref="B185:J186"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
